--- a/docs/downloads/04/tbl_other_chars_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_chars_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -484,12 +484,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -548,12 +542,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -658,12 +646,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -947,7 +929,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D28">
@@ -996,12 +978,6 @@
           <t>Veuf(ve)</t>
         </is>
       </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1085,14 +1061,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="35">
@@ -1108,14 +1084,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="E35">
-        <v>0.5</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="36">
@@ -1131,20 +1107,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D36">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>33.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1154,14 +1130,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="E37">
-        <v>3.2</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="38">
@@ -1177,14 +1153,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D38">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E38">
-        <v>40.3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="39">
@@ -1200,7 +1176,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D39">
@@ -1223,14 +1199,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="41">
@@ -1246,14 +1222,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="E41">
-        <v>2.9</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="42">
@@ -1269,20 +1245,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D42">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>41.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1292,14 +1268,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="E43">
-        <v>2.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -1315,14 +1291,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D44">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="E44">
-        <v>40</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="45">
@@ -1338,14 +1314,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D45">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E45">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="46">
@@ -1361,14 +1337,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="47">
@@ -1384,14 +1360,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="E47">
-        <v>3.1</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="48">
@@ -1407,20 +1383,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1430,20 +1406,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D49">
-        <v>83</v>
+        <v>348</v>
       </c>
       <c r="E49">
-        <v>42.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1453,14 +1429,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E50">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="51">
@@ -1476,14 +1452,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D51">
-        <v>348</v>
+        <v>46</v>
       </c>
       <c r="E51">
-        <v>41.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="52">
@@ -1499,14 +1475,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D52">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E52">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="53">
@@ -1522,14 +1498,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D53">
-        <v>46</v>
+        <v>339</v>
       </c>
       <c r="E53">
-        <v>5.5</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="54">
@@ -1545,82 +1521,13 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D54">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E54">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Marié(e) religieusement</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>3</v>
-      </c>
-      <c r="E55">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Marié(e) selon la tradition</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>339</v>
-      </c>
-      <c r="E56">
-        <v>40.3</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>21</v>
-      </c>
-      <c r="E57">
         <v>2.5</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_other_chars_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_chars_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -546,7 +546,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -569,7 +569,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,7 +592,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -690,7 +690,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -790,7 +790,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -896,7 +896,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -942,7 +942,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1166,7 +1166,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1212,7 +1212,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1258,7 +1258,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1350,7 +1350,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1442,7 +1442,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1488,7 +1488,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">

--- a/docs/downloads/04/tbl_other_chars_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_chars_marovoay_tous.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="26">
@@ -878,7 +878,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -890,7 +890,7 @@
         <v>20</v>
       </c>
       <c r="E26">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -901,7 +901,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -959,7 +959,7 @@
         <v>107</v>
       </c>
       <c r="E29">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="30">
@@ -970,7 +970,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="D31">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E31">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="32">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1022,7 +1022,7 @@
         <v>12</v>
       </c>
       <c r="E32">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="34">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1068,7 +1068,7 @@
         <v>10</v>
       </c>
       <c r="E34">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1091,7 +1091,7 @@
         <v>64</v>
       </c>
       <c r="E35">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="36">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="D37">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E37">
-        <v>40.3</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="38">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1160,7 +1160,7 @@
         <v>13</v>
       </c>
       <c r="E38">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="39">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1183,7 +1183,7 @@
         <v>13</v>
       </c>
       <c r="E39">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="40">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1229,7 +1229,7 @@
         <v>85</v>
       </c>
       <c r="E41">
-        <v>41.3</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="42">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D49">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E49">
-        <v>41.3</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="50">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1505,7 +1505,7 @@
         <v>339</v>
       </c>
       <c r="E53">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="54">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
